--- a/source/WSU/GF_WSU.xlsx
+++ b/source/WSU/GF_WSU.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1234414/Desktop/TEAMS/GF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD3DD2B-918E-9B4C-BDA2-230AA4B5E3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C55BB05-0330-4967-A867-1B0654D33F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32700" yWindow="8180" windowWidth="26840" windowHeight="15760" firstSheet="1" activeTab="1" xr2:uid="{A6913859-4313-D74F-92D6-E15C0C9396E9}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="2" r:id="rId1"/>
-    <sheet name="growth facility list" sheetId="1" r:id="rId2"/>
+    <sheet name="growth facility" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -72,50 +72,50 @@
     <t>For any questions, please contact Liliana Andres at liliana.andreshernandez@adelaide.edu.au.</t>
   </si>
   <si>
+    <t>organisation</t>
+  </si>
+  <si>
+    <t>growth facility name *</t>
+  </si>
+  <si>
+    <t>growth facility description *</t>
+  </si>
+  <si>
+    <t>growth facility type *</t>
+  </si>
+  <si>
+    <t>growth facility type brand *</t>
+  </si>
+  <si>
+    <t>growth facility model *</t>
+  </si>
+  <si>
+    <t>growth facility serial number *</t>
+  </si>
+  <si>
+    <t>containment level *</t>
+  </si>
+  <si>
+    <t>quarantine details *</t>
+  </si>
+  <si>
+    <t>growth facility ontology label</t>
+  </si>
+  <si>
+    <t>growth facility ontology ID</t>
+  </si>
+  <si>
+    <t>growth facility ontology IRI</t>
+  </si>
+  <si>
     <t>WSU</t>
-  </si>
-  <si>
-    <t>organization</t>
-  </si>
-  <si>
-    <t>growth facility name *</t>
-  </si>
-  <si>
-    <t>growth facility description *</t>
-  </si>
-  <si>
-    <t>growth facility type *</t>
-  </si>
-  <si>
-    <t>growth facility type brand *</t>
-  </si>
-  <si>
-    <t>growth facility model *</t>
-  </si>
-  <si>
-    <t>growth facility serial number *</t>
-  </si>
-  <si>
-    <t>containment level *</t>
-  </si>
-  <si>
-    <t>quarantine *</t>
-  </si>
-  <si>
-    <t>growth facility ontology label</t>
-  </si>
-  <si>
-    <t>growth facility ontology ID</t>
-  </si>
-  <si>
-    <t>growth facility ontology IRI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -149,20 +149,8 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="20"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -181,25 +169,17 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -282,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -295,31 +275,26 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -671,40 +646,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71416FF0-E32D-4733-AE06-CF73202146DA}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="150.33203125" style="8" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="150.375" style="7" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:1" ht="26.1">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="44" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:1" ht="44.1">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-    </row>
-    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-    </row>
-    <row r="5" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="3" spans="1:1" ht="21">
+      <c r="A3" s="8"/>
+    </row>
+    <row r="4" spans="1:1" ht="21">
+      <c r="A4" s="8"/>
+    </row>
+    <row r="5" spans="1:1" ht="21">
+      <c r="A5" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="44" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:1" ht="44.1">
+      <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:1" ht="21">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -715,91 +690,90 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19DD2759-F47D-7340-BB2E-2B881912E678}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="31" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="31" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="5" max="5" width="39.6640625" customWidth="1"/>
+    <col min="5" max="5" width="39.625" customWidth="1"/>
     <col min="7" max="9" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="18.75">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="J1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:12" s="3" customFormat="1" ht="15.95">
+      <c r="A2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="6"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:13" s="3" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="3" customFormat="1" ht="18.95">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C3" s="5"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="15"/>
+      <c r="H3" s="10"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="14"/>
-    </row>
-    <row r="4" spans="1:13" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" spans="1:12" s="3" customFormat="1" ht="15.95">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C4" s="5"/>
     </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="G9" s="4"/>
     </row>
   </sheetData>
@@ -809,6 +783,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Image xmlns="c57c0e25-d6d6-4f5b-b0b2-7d758d7a4949" xsi:nil="true"/>
+    <TaxCatchAll xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23" xsi:nil="true"/>
+    <l544f18d430f4c0886024d9e622455c4 xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </l544f18d430f4c0886024d9e622455c4>
+    <jbe33349d2e04ad58f3e9557e0157918 xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </jbe33349d2e04ad58f3e9557e0157918>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c57c0e25-d6d6-4f5b-b0b2-7d758d7a4949">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <f876555452e44e5798dee990952b63ae xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </f876555452e44e5798dee990952b63ae>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="d560fd02-aa12-447b-bf2e-34c9e57d035a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007EE926928A949E41B5C68441ED11B2EA" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="52be21af1a8349f18767d387bddd8232">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b2ccdccd-44c9-4047-9c28-347bfbb7eb23" xmlns:ns3="c57c0e25-d6d6-4f5b-b0b2-7d758d7a4949" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="10d9f1abffa380d50643d816c40c845c" ns2:_="" ns3:_="">
     <xsd:import namespace="b2ccdccd-44c9-4047-9c28-347bfbb7eb23"/>
@@ -1063,7 +1063,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1072,53 +1072,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Image xmlns="c57c0e25-d6d6-4f5b-b0b2-7d758d7a4949" xsi:nil="true"/>
-    <TaxCatchAll xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23" xsi:nil="true"/>
-    <l544f18d430f4c0886024d9e622455c4 xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </l544f18d430f4c0886024d9e622455c4>
-    <jbe33349d2e04ad58f3e9557e0157918 xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </jbe33349d2e04ad58f3e9557e0157918>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c57c0e25-d6d6-4f5b-b0b2-7d758d7a4949">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <f876555452e44e5798dee990952b63ae xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </f876555452e44e5798dee990952b63ae>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="d560fd02-aa12-447b-bf2e-34c9e57d035a" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5321F6AD-BE4F-4818-A997-2972527598AB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FD0F955-CAD8-4BF8-B22A-B76A997DC893}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58C82CBD-AD96-4033-B381-FEF06DF46847}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65F7B588-5675-4B99-83A0-FB5D6D03E9AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5321F6AD-BE4F-4818-A997-2972527598AB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FD0F955-CAD8-4BF8-B22A-B76A997DC893}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65F7B588-5675-4B99-83A0-FB5D6D03E9AF}"/>
 </file>
--- a/source/WSU/GF_WSU.xlsx
+++ b/source/WSU/GF_WSU.xlsx
@@ -1,53 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1234414/Desktop/TEAMS/GF/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C55BB05-0330-4967-A867-1B0654D33F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="32700" yWindow="8180" windowWidth="26840" windowHeight="15760" firstSheet="1" activeTab="1" xr2:uid="{A6913859-4313-D74F-92D6-E15C0C9396E9}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="2" r:id="rId1"/>
-    <sheet name="growth facility" sheetId="1" r:id="rId2"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="growth facility" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>tc={A2055D20-A51D-4645-B33E-D1F4DFA9B470}</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{A2055D20-A51D-4645-B33E-D1F4DFA9B470}">
+    <comment ref="C1" authorId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Add more details in here, footprint, space, quarantine, PC level.</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -57,129 +48,160 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
-    <t>Template to record Growth facilities information</t>
-  </si>
-  <si>
-    <t>This spreadsheet serves as a template for collecting information and establishing naming conventions for APPN growth facilities and types.</t>
-  </si>
-  <si>
-    <t>1. Please only fill the columns in the growth facility template indicated with an asterisk (*) and highlighted in red. </t>
-  </si>
-  <si>
-    <t>2. We have included some examples of growth facility types in sheet 1. For every growth facility name/ID listed please add a growth facilty type.</t>
-  </si>
-  <si>
-    <t>For any questions, please contact Liliana Andres at liliana.andreshernandez@adelaide.edu.au.</t>
-  </si>
-  <si>
-    <t>organisation</t>
-  </si>
-  <si>
-    <t>growth facility name *</t>
-  </si>
-  <si>
-    <t>growth facility description *</t>
-  </si>
-  <si>
-    <t>growth facility type *</t>
-  </si>
-  <si>
-    <t>growth facility type brand *</t>
-  </si>
-  <si>
-    <t>growth facility model *</t>
-  </si>
-  <si>
-    <t>growth facility serial number *</t>
-  </si>
-  <si>
-    <t>containment level *</t>
-  </si>
-  <si>
-    <t>quarantine details *</t>
-  </si>
-  <si>
-    <t>growth facility ontology label</t>
-  </si>
-  <si>
-    <t>growth facility ontology ID</t>
-  </si>
-  <si>
-    <t>growth facility ontology IRI</t>
-  </si>
-  <si>
-    <t>WSU</t>
+    <t xml:space="preserve">Template to record Growth facilities information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This spreadsheet serves as a template for collecting information and establishing naming conventions for APPN growth facilities and types.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Please only fill the columns in the growth facility template indicated with an asterisk (*) and highlighted in red. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. We have included some examples of growth facility types in sheet 1. For every growth facility name/ID listed please add a growth facilty type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For any questions, please contact Liliana Andres at liliana.andreshernandez@adelaide.edu.au.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">organisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility name *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility description *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility type *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility type brand *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility model *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility serial number *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">containment level *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quarantine details *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility ontology label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility ontology ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility ontology IRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -191,325 +213,328 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.7999"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="5">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
+        <color theme="2" tint="-0.1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.15"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
       </left>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD1D1D1"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD9F2D0"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Liliana Andres Hernandez" id="{A621DC9E-66D4-384B-A9AC-C1238F3B9150}" userId="S::a1234414@adelaide.edu.au::f5ea0ab9-0879-431c-9495-63f7ab505ec3" providerId="AD"/>
-</personList>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -517,33 +542,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -556,13 +572,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -572,15 +582,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -588,7 +596,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -596,189 +603,172 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C1" dT="2026-01-21T00:38:22.28" personId="{A621DC9E-66D4-384B-A9AC-C1238F3B9150}" id="{A2055D20-A51D-4645-B33E-D1F4DFA9B470}">
-    <text>Add more details in here, footprint, space, quarantine, PC level.</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71416FF0-E32D-4733-AE06-CF73202146DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.95"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="150.375" style="7" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="150.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="26.1">
-      <c r="A1" s="6" t="s">
+    <row r="1" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="44.1">
-      <c r="A2" s="8" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="21">
-      <c r="A3" s="8"/>
-    </row>
-    <row r="4" spans="1:1" ht="21">
-      <c r="A4" s="8"/>
-    </row>
-    <row r="5" spans="1:1" ht="21">
-      <c r="A5" s="9" t="s">
+    <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="44.1">
-      <c r="A6" s="8" t="s">
+    <row r="6" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="21">
-      <c r="A7" s="9" t="s">
+    <row r="7" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19DD2759-F47D-7340-BB2E-2B881912E678}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="31" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="31" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="5" max="5" width="39.625" customWidth="1"/>
-    <col min="7" max="9" width="40.5" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="39.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="40.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="18.75">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="5" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="3" customFormat="1" ht="15.95">
-      <c r="A2" s="3" t="s">
+    <row r="2" s="10" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:12" s="3" customFormat="1" ht="18.95">
-      <c r="A3" s="3" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+    </row>
+    <row r="3" s="10" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" ht="15.95">
-      <c r="A4" s="3" t="s">
+      <c r="C3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" s="10" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="G9" s="4"/>
+      <c r="C4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G9" s="11"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
